--- a/diagnostics/survivorship_sheet_research.xlsx
+++ b/diagnostics/survivorship_sheet_research.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,104 +694,104 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>reference index: CAGR</t>
+          <t>NSE index: CAGR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>reference index: MaxDD</t>
+          <t>NSE index: MaxDD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-48.95</t>
+          <t>-46.31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-37.67</t>
+          <t>-38.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-38.89</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-37.92</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-38.03</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.60</t>
+          <t>-57.47</t>
         </is>
       </c>
     </row>
@@ -1000,6 +1000,110 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>-7.86 (from 2021-10-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): CAGR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26.56</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): MaxDD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-48.95</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-37.67</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-38.89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-37.92</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-41.56</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-38.03</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-37.40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-37.31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-48.60</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,104 +1384,104 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>reference index: CAGR</t>
+          <t>NSE index: CAGR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>reference index: MaxDD</t>
+          <t>NSE index: MaxDD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-48.95</t>
+          <t>-46.31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-37.67</t>
+          <t>-38.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-38.89</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-37.92</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-38.03</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.60</t>
+          <t>-57.47</t>
         </is>
       </c>
     </row>
@@ -1586,6 +1690,110 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>-4.09 (from 2021-10-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): CAGR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26.56</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): MaxDD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-48.95</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-37.67</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-38.89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-37.92</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-41.56</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-38.03</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-37.40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-37.31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-48.60</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,104 +2074,104 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>reference index: CAGR</t>
+          <t>NSE index: CAGR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>reference index: MaxDD</t>
+          <t>NSE index: MaxDD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-48.95</t>
+          <t>-46.31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-37.67</t>
+          <t>-38.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-38.89</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-37.92</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-38.03</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.60</t>
+          <t>-57.47</t>
         </is>
       </c>
     </row>
@@ -2172,6 +2380,110 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>-8.43 (from 2021-10-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): CAGR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26.56</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): MaxDD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-48.95</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-37.67</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-38.89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-37.92</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-41.56</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-38.03</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-37.40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-37.31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-48.60</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,104 +2764,104 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>reference index: CAGR</t>
+          <t>NSE index: CAGR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>reference index: MaxDD</t>
+          <t>NSE index: MaxDD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-48.95</t>
+          <t>-46.31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-37.67</t>
+          <t>-38.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-38.89</t>
+          <t>-40.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-37.92</t>
+          <t>-43.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-41.56</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-38.03</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.60</t>
+          <t>-57.47</t>
         </is>
       </c>
     </row>
@@ -2758,6 +3070,110 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>-5.04 (from 2021-10-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): CAGR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26.56</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25.60</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>23.91</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>equal-weight basket (untaxed, daily rebalanced): MaxDD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-48.95</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-37.67</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-38.89</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-37.92</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-41.56</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-38.03</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-37.40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-37.31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-48.60</t>
         </is>
       </c>
     </row>

--- a/diagnostics/survivorship_sheet_research.xlsx
+++ b/diagnostics/survivorship_sheet_research.xlsx
@@ -543,47 +543,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>38.44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>28.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.29</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.90</t>
+          <t>48.76</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.34 (from 2021-10-29)</t>
+          <t>25.15 (from 2021-10-29)</t>
         </is>
       </c>
     </row>
@@ -647,47 +647,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.70</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>30.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>33.10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>43.30</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1243,37 +1243,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.57</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.15 (from 2021-10-29)</t>
+          <t>18.04 (from 2021-10-29)</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>27.40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>26.90</t>
         </is>
       </c>
     </row>
@@ -1923,47 +1923,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.36</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>12.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.81 (from 2021-10-29)</t>
+          <t>30.54 (from 2021-10-29)</t>
         </is>
       </c>
     </row>
@@ -2027,47 +2027,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.99</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.92</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>36.50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>55.53</t>
         </is>
       </c>
     </row>
@@ -2613,47 +2613,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>21.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>17.66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.35 (from 2021-10-29)</t>
+          <t>25.17 (from 2021-10-29)</t>
         </is>
       </c>
     </row>
@@ -2717,47 +2717,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.27</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>23.10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>33.08</t>
         </is>
       </c>
     </row>

--- a/diagnostics/survivorship_sheet_research.xlsx
+++ b/diagnostics/survivorship_sheet_research.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>microcap250</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mcapover10000</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -534,6 +549,21 @@
           <t>30.00 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -586,6 +616,21 @@
           <t>25.15 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -638,6 +683,21 @@
           <t>53.07</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>54.03</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>62.82</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>48.71</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -690,6 +750,21 @@
           <t>43.30</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>44.31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>53.28</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>41.05</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -742,6 +817,21 @@
           <t>21.27</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -794,6 +884,21 @@
           <t>-57.47</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -846,6 +951,21 @@
           <t>-42.45</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-41.52</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-34.26</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-32.59</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -898,6 +1018,21 @@
           <t>-6.51</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-6.33</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-4.39</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -950,6 +1085,21 @@
           <t>-31.54 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1002,6 +1152,21 @@
           <t>-7.86 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1054,6 +1219,21 @@
           <t>27.89</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>146.88</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28.67</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>25.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1104,6 +1284,69 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>-48.60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-49.75</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-48.69</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-40.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NOTE mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NOTE mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 216 names as a market-cap bucket, with no membership history. Only 0 of the 216 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NOTE mcapover10000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 538 names as a market-cap bucket, with no membership history. Only 2 of the 538 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1415,21 @@
           <t>microcap250</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mcapover10000</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1224,6 +1482,21 @@
           <t>21.46 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1276,6 +1549,21 @@
           <t>18.04 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1328,6 +1616,21 @@
           <t>32.11</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>27.82</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>39.04</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>32.77</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1380,6 +1683,21 @@
           <t>26.90</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23.46</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>32.70</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>27.66</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1432,6 +1750,21 @@
           <t>21.27</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1484,6 +1817,21 @@
           <t>-57.47</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1536,6 +1884,21 @@
           <t>-22.63</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-21.92</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-20.88</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-18.59</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1588,6 +1951,21 @@
           <t>-3.71</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-4.67</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-3.01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1640,6 +2018,21 @@
           <t>-13.56 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1692,6 +2085,21 @@
           <t>-4.09 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1744,6 +2152,21 @@
           <t>27.89</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>146.88</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28.67</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>25.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1794,6 +2217,69 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>-48.60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-49.75</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-48.69</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-40.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NOTE mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NOTE mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 216 names as a market-cap bucket, with no membership history. Only 0 of the 216 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NOTE mcapover10000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 538 names as a market-cap bucket, with no membership history. Only 2 of the 538 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -1808,7 +2294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +2348,21 @@
           <t>microcap250</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mcapover10000</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1914,6 +2415,21 @@
           <t>37.07 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1966,6 +2482,21 @@
           <t>30.54 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2018,6 +2549,21 @@
           <t>67.11</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>58.54</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>53.65</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>53.22</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2070,6 +2616,21 @@
           <t>55.53</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>49.82</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>46.45</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>44.94</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2122,6 +2683,21 @@
           <t>21.27</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2174,6 +2750,21 @@
           <t>-57.47</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2226,6 +2817,21 @@
           <t>-40.97</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-50.93</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-38.72</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-35.21</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2278,6 +2884,21 @@
           <t>-8.43</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-7.90</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-8.09</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-6.65</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2330,6 +2951,21 @@
           <t>-32.46 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2382,6 +3018,21 @@
           <t>-8.43 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2434,6 +3085,21 @@
           <t>27.89</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>146.88</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28.67</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>25.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2484,6 +3150,69 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>-48.60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-49.75</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-48.69</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-40.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NOTE mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NOTE mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 216 names as a market-cap bucket, with no membership history. Only 0 of the 216 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NOTE mcapover10000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 538 names as a market-cap bucket, with no membership history. Only 2 of the 538 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -2498,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +3281,21 @@
           <t>microcap250</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mcapover10000</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -2604,6 +3348,21 @@
           <t>30.07 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2656,6 +3415,21 @@
           <t>25.17 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2708,6 +3482,21 @@
           <t>39.41</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>30.59</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>37.83</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>34.87</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2760,6 +3549,21 @@
           <t>33.08</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25.78</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>31.88</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>29.62</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2812,6 +3616,21 @@
           <t>21.27</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.94</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2864,6 +3683,21 @@
           <t>-57.47</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-38.30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2916,6 +3750,21 @@
           <t>-20.61</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-31.29</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-24.68</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-22.05</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2968,6 +3817,21 @@
           <t>-5.25</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-5.44</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-5.05</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-4.72</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3020,6 +3884,21 @@
           <t>-17.93 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3072,6 +3951,21 @@
           <t>-5.04 (from 2021-10-29)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>not available: no membership file for this supplier bucket</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3124,6 +4018,21 @@
           <t>27.89</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>146.88</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28.67</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>25.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3174,6 +4083,69 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>-48.60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-49.75</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-48.69</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-40.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NOTE mcap1500to5000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NOTE mcap5001to10000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 216 names as a market-cap bucket, with no membership history. Only 0 of the 216 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NOTE mcapover10000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 538 names as a market-cap bucket, with no membership history. Only 2 of the 538 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>

--- a/diagnostics/survivorship_sheet_research.xlsx
+++ b/diagnostics/survivorship_sheet_research.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-41.52</t>
+          <t>-40.93</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>146.88</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-49.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 477 names as a market-cap bucket, with no membership history. Only 2 of the 477 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-21.92</t>
+          <t>-17.68</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>146.88</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-49.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 477 names as a market-cap bucket, with no membership history. Only 2 of the 477 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>49.84</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-50.93</t>
+          <t>-49.16</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>146.88</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-49.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 477 names as a market-cap bucket, with no membership history. Only 2 of the 477 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>146.88</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-49.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STATIC AND NOT AN INDEX. The supplier delivered these 478 names as a market-cap bucket, with no membership history. Only 2 of the 478 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
+          <t>STATIC AND NOT AN INDEX. The supplier delivered these 477 names as a market-cap bucket, with no membership history. Only 2 of the 477 stop trading before the window ends, so the list appears to hold the bucket's members near the time of delivery, not the members at each date. A stock that left the bucket or was delisted is likely missing; a stock that grew into it is present for the whole window. Both the strategy and its buy &amp; hold therefore likely carry survivorship and look-ahead bias, which cannot be measured without membership files. The benchmark index is the broad NIFTY 500, not a bucket index.</t>
         </is>
       </c>
     </row>

--- a/diagnostics/survivorship_sheet_research.xlsx
+++ b/diagnostics/survivorship_sheet_research.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.90</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.40</t>
+          <t>57.12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>38.44</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.76</t>
+          <t>48.53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>62.82</t>
+          <t>61.96</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>37.69</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-40.93</t>
+          <t>-42.64</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>32.40</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>39.07</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>23.60</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-17.68</t>
+          <t>-17.32</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-20.88</t>
+          <t>-20.86</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>58.32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.88</t>
+          <t>58.58</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>49.99</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>53.54</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>54.06</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>49.84</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-49.16</t>
+          <t>-49.14</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-38.72</t>
+          <t>-38.53</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>27.20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>33.79</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>32.30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>-21.04</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-24.68</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
